--- a/outputs/clean_score.xlsx
+++ b/outputs/clean_score.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>88.8</v>
+        <v>89.7333333333</v>
       </c>
       <c r="D3" t="n">
         <v>98</v>
@@ -505,7 +505,7 @@
         <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>82.25</v>
+        <v>78.6666666667</v>
       </c>
       <c r="G3" t="n">
         <v>89</v>
@@ -539,7 +539,35 @@
         <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>422</v>
+        <v>460</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>罗明</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D5" t="n">
+        <v>96</v>
+      </c>
+      <c r="E5" t="n">
+        <v>85</v>
+      </c>
+      <c r="F5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G5" t="n">
+        <v>91</v>
+      </c>
+      <c r="H5" t="n">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
